--- a/数据表/Const.xlsx
+++ b/数据表/Const.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="const" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>//注释</t>
   </si>
@@ -64,19 +64,16 @@
     <t>string</t>
   </si>
   <si>
-    <t>guankadaojishi</t>
-  </si>
-  <si>
-    <t>普通关卡倒计时时间单位秒</t>
-  </si>
-  <si>
-    <t>guankadiaoxingshijian</t>
-  </si>
-  <si>
-    <t>90,60,30</t>
-  </si>
-  <si>
-    <t>普通关卡掉星剩余时间，每剩余到这个时间掉1星：格式：时间，时间，时间</t>
+    <t>zongbingli</t>
+  </si>
+  <si>
+    <t>关卡双方兵力值上限</t>
+  </si>
+  <si>
+    <t>juezhanshijian</t>
+  </si>
+  <si>
+    <t>关卡决战开始时间</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1112,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -1128,11 +1125,12 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5">
+        <v>300</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
